--- a/proyecto-asul/fase-06-normatividad/checklist-cliente.xlsx
+++ b/proyecto-asul/fase-06-normatividad/checklist-cliente.xlsx
@@ -772,17 +772,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>⚠️ (sin información)</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>La entrevista se cerró antes de que esta pregunta fuera respondida por el cliente</t>
+          <t>El cliente confirmó explícitamente (octubre 2026) que no es necesario cumplir ninguna normativa o circular sectorial específica como condición del contrato.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Completar esta pregunta en una próxima sesión con el cliente antes de cerrar el taller</t>
+          <t>Ninguna acción requerida; revisar si esto cambia ante nuevos contratos con clientes de un sector más regulado.</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,52 +911,25 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Normatividad sectorial</t>
+          <t>Gobierno de datos</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>No se confirmó si el cliente exige cumplir alguna normativa o circular específica del sector financiero/asegurador como condición contractual</t>
+          <t>No se identificó un responsable formal (rol de oficial de protección de datos o equivalente) más allá de políticas generales</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Posible incumplimiento contractual o regulatorio no identificado (por ejemplo, circulares de la Superintendencia Financiera) si el cliente sí lo exige</t>
+          <t>Falta de un punto único de responsabilidad ante una solicitud o un incidente relacionado con datos personales</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Completar esta pregunta con el cliente antes de cerrar el taller; revisar el contrato marco vigente con Rentec</t>
+          <t>Asignar formalmente el rol de responsable de protección de datos, aunque sea como función adicional de un cargo existente</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno de datos</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>No se identificó un responsable formal (rol de oficial de protección de datos o equivalente) más allá de políticas generales</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Falta de un punto único de responsabilidad ante una solicitud o un incidente relacionado con datos personales</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Asignar formalmente el rol de responsable de protección de datos, aunque sea como función adicional de un cargo existente</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
